--- a/docs/valuation-models.xlsx
+++ b/docs/valuation-models.xlsx
@@ -190,12 +190,12 @@
   <commentList>
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
-        <t>freeCashflow, snapshot Jul 16, 2026. Trailing FCF is capex-depressed: net income is $125.216B.</t>
+        <t>Trailing twelve months: operating cash flow minus capex, summed from the last four quarterly cash-flow statements. Snapshot Sep 17, 2026. Net income over the same period is $133.749B.</t>
       </text>
     </comment>
     <comment ref="B8" authorId="0" shapeId="0">
       <text>
-        <t>Deliberate lever. Snapshot trailing revenue growth is 18.3% — 10% assumes FCF grows below revenue while capex stays elevated.</t>
+        <t>Deliberate lever. Snapshot fiscal-year revenue growth is 17.8% — 10% assumes FCF grows below revenue while capex stays elevated.</t>
       </text>
     </comment>
     <comment ref="B9" authorId="0" shapeId="0">
@@ -210,7 +210,7 @@
     </comment>
     <comment ref="B11" authorId="0" shapeId="0">
       <text>
-        <t>totalDebt 125.432B − totalCash 78.228B, snapshot.</t>
+        <t>totalDebt 128.813B − totalCash 76.843B, snapshot.</t>
       </text>
     </comment>
   </commentList>
@@ -225,7 +225,7 @@
   <commentList>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>totalDebt 64.907B − totalCash 19.628B, snapshot.</t>
+        <t>totalDebt 59.419B − totalCash 23.975B, snapshot.</t>
       </text>
     </comment>
   </commentList>
@@ -550,7 +550,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Jul 16, 2026</t>
+          <t>Sep 17, 2026</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>37.011</v>
+        <v>66.98699999999999</v>
       </c>
     </row>
     <row r="8">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>47.204</v>
+        <v>51.97</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2938.912</v>
+        <v>3640.745</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>395.63</v>
+        <v>490.3</v>
       </c>
     </row>
     <row r="14">
@@ -888,14 +888,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Reading the gap: trailing FCF is capex-depressed (net income ~3x FCF in the snapshot), so a</t>
+          <t>Reading the gap: the base case compounds trailing FCF at a flat rate with no margin expansion,</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>conservative trailing-FCF DCF reads far below market — the price embeds AI-cycle FCF normalization.</t>
+          <t>so it reads below market. Net income is 2.0x trailing FCF — this model values cash conversion, not accounting profit.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot Jul 16, 2026 from the pipeline (data.json). Peers = universe members with industry 'Semiconductors' — a finer peer set than the sector-level medians the site computes.</t>
+          <t>Snapshot Sep 17, 2026 from the pipeline (data.json). Peers = universe members with industry 'Semiconductors' — a finer peer set than the sector-level medians the site computes.</t>
         </is>
       </c>
     </row>
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>212.5</v>
+        <v>213.9</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>5146.963</v>
+        <v>5165.043</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5102.142</v>
+        <v>5131.381</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>30.826</v>
+        <v>25.496</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>16.595171</v>
+        <v>13.698463</v>
       </c>
       <c r="H5" s="10">
         <f>E5/F5</f>
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>529.14</v>
+        <v>512.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>862.816</v>
+        <v>836.643</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>854.34</v>
+        <v>827.808</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>114.985</v>
+        <v>86.57299999999999</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>39.69367</v>
+        <v>32.914406</v>
       </c>
       <c r="H6" s="10">
         <f>E6/F6</f>
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>102.99</v>
+        <v>101.05</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>517.628</v>
+        <v>534.1609999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>543.465</v>
+        <v>546.107</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>38.342</v>
+        <v>32.429</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>64.667435</v>
+        <v>49.00392</v>
       </c>
       <c r="H7" s="10">
         <f>E7/F7</f>
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>177.98</v>
+        <v>184.84</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>187.591</v>
+        <v>197.42</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>193.062</v>
+        <v>201.091</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>14.852</v>
+        <v>16.759</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>16.116777</v>
+        <v>18.114447</v>
       </c>
       <c r="H8" s="10">
         <f>E8/F8</f>
@@ -1293,19 +1293,19 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>301.19</v>
+        <v>260.67</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>274.111</v>
+        <v>238.056</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>283.058</v>
+        <v>245.107</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>32.667</v>
+        <v>25.747</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>31.461296</v>
+        <v>24.4879</v>
       </c>
       <c r="H9" s="10">
         <f>E9/F9</f>
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>579.4299999999999</v>
+        <v>415.38</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>460.044</v>
+        <v>329.645</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>459.071</v>
+        <v>327.757</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>49.496</v>
+        <v>32.275</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>34.601883</v>
+        <v>22.507978</v>
       </c>
       <c r="H10" s="10">
         <f>E10/F10</f>
@@ -1363,19 +1363,19 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>904.28</v>
+        <v>926.55</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1021.288</v>
+        <v>1046.439</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1001.642</v>
+        <v>1026.793</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>14.682</v>
+        <v>15.051</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>6.0098834</v>
+        <v>5.9265184</v>
       </c>
       <c r="H11" s="10">
         <f>E11/F11</f>
@@ -1398,19 +1398,19 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>390.96</v>
+        <v>362.04</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>190.432</v>
+        <v>175.432</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>195.701</v>
+        <v>182.271</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>31.824</v>
+        <v>26.329</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>26.066711</v>
+        <v>22.145666</v>
       </c>
       <c r="H12" s="10">
         <f>E12/F12</f>
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>335.43</v>
+        <v>269.23</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>419.479</v>
+        <v>336.893</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>418.463</v>
+        <v>335.436</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>53.323</v>
+        <v>38.818</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>41.504932</v>
+        <v>23.106222</v>
       </c>
       <c r="H13" s="10">
         <f>E13/F13</f>
@@ -1468,19 +1468,19 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>224.5</v>
+        <v>167.36</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>293.259</v>
+        <v>218.664</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>294.446</v>
+        <v>219.913</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>50.331</v>
+        <v>36.321</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>43.84509</v>
+        <v>24.959026</v>
       </c>
       <c r="H14" s="10">
         <f>E14/F14</f>
@@ -1503,19 +1503,19 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>206.26</v>
+        <v>229.71</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>185.128</v>
+        <v>206.441</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>181.87</v>
+        <v>202.786</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>67.06100000000001</v>
+        <v>71.145</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>33.27096</v>
+        <v>33.976498</v>
       </c>
       <c r="H15" s="10">
         <f>E15/F15</f>
@@ -1558,19 +1558,19 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>394.28</v>
+        <v>339.51</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1875.819</v>
+        <v>1620.695</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1921.098</v>
+        <v>1656.139</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>45.649</v>
+        <v>31.69</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>20.30602</v>
+        <v>17.515043</v>
       </c>
       <c r="H18" s="10">
         <f>E18/F18</f>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>45.279</v>
+        <v>35.444</v>
       </c>
     </row>
     <row r="21">

--- a/docs/valuation-models.xlsx
+++ b/docs/valuation-models.xlsx
@@ -190,7 +190,7 @@
   <commentList>
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
-        <t>Trailing twelve months: operating cash flow minus capex, summed from the last four quarterly cash-flow statements. Snapshot Sep 17, 2026. Net income over the same period is $133.749B.</t>
+        <t>Trailing twelve months: operating cash flow minus capex, summed from the last four quarterly cash-flow statements. Snapshot Sep 23, 2026. Net income over the same period is $133.749B.</t>
       </text>
     </comment>
     <comment ref="B8" authorId="0" shapeId="0">
@@ -550,7 +550,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Sep 17, 2026</t>
+          <t>Sep 23, 2026</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>3640.745</v>
+        <v>3697.922</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>490.3</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot Sep 17, 2026 from the pipeline (data.json). Peers = universe members with industry 'Semiconductors' — a finer peer set than the sector-level medians the site computes.</t>
+          <t>Snapshot Sep 23, 2026 from the pipeline (data.json). Peers = universe members with industry 'Semiconductors' — a finer peer set than the sector-level medians the site computes.</t>
         </is>
       </c>
     </row>
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>213.9</v>
+        <v>228.87</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>5165.043</v>
+        <v>5526.523</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5131.381</v>
+        <v>5492.158</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>25.496</v>
+        <v>27.288</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>13.698463</v>
+        <v>14.593853</v>
       </c>
       <c r="H5" s="10">
         <f>E5/F5</f>
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>512.5</v>
+        <v>623.77</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>836.643</v>
+        <v>1018.289</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>827.808</v>
+        <v>1009.454</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>86.57299999999999</v>
+        <v>105.569</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>32.914406</v>
+        <v>40.060524</v>
       </c>
       <c r="H6" s="10">
         <f>E6/F6</f>
@@ -1223,19 +1223,19 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>101.05</v>
+        <v>123.86</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>534.1609999999999</v>
+        <v>654.737</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>546.107</v>
+        <v>661.1609999999999</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>32.429</v>
+        <v>39.261</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>49.00392</v>
+        <v>60.065567</v>
       </c>
       <c r="H7" s="10">
         <f>E7/F7</f>
@@ -1258,19 +1258,19 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>184.84</v>
+        <v>198.27</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>197.42</v>
+        <v>211.764</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>201.091</v>
+        <v>215.196</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>16.759</v>
+        <v>17.934</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>18.114447</v>
+        <v>19.430597</v>
       </c>
       <c r="H8" s="10">
         <f>E8/F8</f>
@@ -1293,19 +1293,19 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>260.67</v>
+        <v>271.41</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>238.056</v>
+        <v>247.865</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>245.107</v>
+        <v>254.916</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>25.747</v>
+        <v>26.777</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>24.4879</v>
+        <v>25.496838</v>
       </c>
       <c r="H9" s="10">
         <f>E9/F9</f>
@@ -1328,19 +1328,19 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>415.38</v>
+        <v>472.46</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>329.645</v>
+        <v>374.943</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>327.757</v>
+        <v>373.056</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>32.275</v>
+        <v>36.736</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>22.507978</v>
+        <v>25.60094</v>
       </c>
       <c r="H10" s="10">
         <f>E10/F10</f>
@@ -1363,19 +1363,19 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>926.55</v>
+        <v>1096.16</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1046.439</v>
+        <v>1237.996</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1026.793</v>
+        <v>1218.35</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>15.051</v>
+        <v>17.859</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>5.9265184</v>
+        <v>6.8972793</v>
       </c>
       <c r="H11" s="10">
         <f>E11/F11</f>
@@ -1398,19 +1398,19 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>362.04</v>
+        <v>390.37</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>175.432</v>
+        <v>189.16</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>182.271</v>
+        <v>195.999</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>26.329</v>
+        <v>28.312</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>22.145666</v>
+        <v>23.878586</v>
       </c>
       <c r="H12" s="10">
         <f>E12/F12</f>
@@ -1433,19 +1433,19 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>269.23</v>
+        <v>310.96</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>336.893</v>
+        <v>389.111</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>335.436</v>
+        <v>387.653</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>38.818</v>
+        <v>44.86</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>23.106222</v>
+        <v>26.48826</v>
       </c>
       <c r="H13" s="10">
         <f>E13/F13</f>
@@ -1468,19 +1468,19 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>167.36</v>
+        <v>188.32</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>218.664</v>
+        <v>246.049</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>219.913</v>
+        <v>247.298</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>36.321</v>
+        <v>40.844</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>24.959026</v>
+        <v>28.08487</v>
       </c>
       <c r="H14" s="10">
         <f>E14/F14</f>
@@ -1503,19 +1503,19 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>229.71</v>
+        <v>262.36</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>206.441</v>
+        <v>235.784</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>202.786</v>
+        <v>231.417</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>71.145</v>
+        <v>81.19</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>33.976498</v>
+        <v>38.826443</v>
       </c>
       <c r="H15" s="10">
         <f>E15/F15</f>
@@ -1558,19 +1558,19 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>339.51</v>
+        <v>364.54</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1620.695</v>
+        <v>1740.179</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1656.139</v>
+        <v>1775.623</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>31.69</v>
+        <v>33.977</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>17.515043</v>
+        <v>18.80632</v>
       </c>
       <c r="H18" s="10">
         <f>E18/F18</f>
